--- a/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,0</t>
+          <t>-6,82; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,87</t>
+          <t>-1,81; 4,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,19</t>
+          <t>-0,88; 0,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,19</t>
+          <t>-1,37; 0,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,76</t>
+          <t>-0,45; 0,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,59</t>
+          <t>-100,0; 220,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,62</t>
+          <t>-0,39; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; -0,08</t>
+          <t>-1,3; -0,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,66</t>
+          <t>-0,33; 0,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,9</t>
+          <t>-100,0; 36,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 0,0</t>
+          <t>-6,18; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,81</t>
+          <t>-1,89; 4,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,2</t>
+          <t>-1,36; 0,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,71</t>
+          <t>-0,55; 0,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,27</t>
+          <t>-100,0; 175,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,57</t>
+          <t>-0,38; 0,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; -0,06</t>
+          <t>-1,34; -0,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,59</t>
+          <t>-0,38; 0,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,85</t>
+          <t>-100,0; 75,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,0</t>
+          <t>-8,11; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,04</t>
+          <t>-1,86; 4,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,32</t>
+          <t>-0,97; 0,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,18</t>
+          <t>-1,34; 0,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,71</t>
+          <t>-0,48; 0,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 175,02</t>
+          <t>-100,0; 227,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,0</t>
+          <t>-2,05; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,59</t>
+          <t>-0,38; 0,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; -0,05</t>
+          <t>-1,4; -0,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,63</t>
+          <t>-0,35; 0,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,81</t>
+          <t>-100,0; 30,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1006-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,145 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>107,2%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.458327233769463</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.38310888954622</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.989762820407951</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.071973325880401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,11; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 4,87</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.108534957385363</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.861120790996517</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.39694504630867</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.865341389707286</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-63,91%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-63,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,97; 0,19</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,34; 0,19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 0,76</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 227,59</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.2813828328860327</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.5264926708661932</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.0460070121635018</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.6391319868084081</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.6376099051698852</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1646646477423674</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.9654937684492962</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.344133929704184</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.4791694848024939</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,51</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,05; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.186422048764841</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1909659287803282</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7565804179401882</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>2.275911886452405</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +749,137 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-75,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3007993077296526</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3889169538687847</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 0,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,4; -0,08</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 0,66</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 30,9</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.045921935606505</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.511026986907943</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.0776655474161231</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5974109775839964</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1110770308573143</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.267013175273511</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7583624456186502</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.4138745132289368</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.3806025156090285</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.401463611690288</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.3488365167655252</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6187797127252783</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.07863285852599487</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6565341321135393</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>0.3089919056105646</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +888,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
